--- a/artfynd/A 29826-2023 artfynd.xlsx
+++ b/artfynd/A 29826-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +785,728 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120398735</v>
+      </c>
+      <c r="B3" t="n">
+        <v>94704</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bråtaskogen A 29826-2023, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>328669</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6397391</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Råda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Några större kuddar.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120398654</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57689</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bråtaskogen A 29826-2023, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>328663</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6397152</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Råda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Minst 2 ex.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120401028</v>
+      </c>
+      <c r="B5" t="n">
+        <v>94701</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>535</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skuggmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dicranodontium denudatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brid.) E.Britton</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bråtaskogen A 29826-2023, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>328675</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6397260</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Råda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Några kuddar på sten.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120401154</v>
+      </c>
+      <c r="B6" t="n">
+        <v>94701</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>535</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skuggmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dicranodontium denudatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brid.) E.Britton</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bråtaskogen A 29826-2023, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>328669</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6397391</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Råda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På rotben, äldre gran. En tuva.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120398482</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57689</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bråtaskogen A 29826-2023, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>328560</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6397125</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Råda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120398521</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bråtaskogen A 29826-2023, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>328560</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6397300</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Råda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Kom inflygande och landade.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29826-2023 artfynd.xlsx
+++ b/artfynd/A 29826-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120398735</v>
+        <v>120398654</v>
       </c>
       <c r="B3" t="n">
-        <v>94704</v>
+        <v>57689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,27 +803,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>328669</v>
+        <v>328663</v>
       </c>
       <c r="R3" t="n">
-        <v>6397391</v>
+        <v>6397152</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,14 +872,24 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Några större kuddar.</t>
+          <t>Minst 2 ex.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,7 +898,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120398654</v>
+        <v>120398735</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>94704</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +932,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>328663</v>
+        <v>328669</v>
       </c>
       <c r="R4" t="n">
-        <v>6397152</v>
+        <v>6397391</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,24 +993,14 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 2 ex.</t>
+          <t>Några större kuddar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,6 +1009,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120401028</v>
+        <v>120398482</v>
       </c>
       <c r="B5" t="n">
-        <v>94701</v>
+        <v>57689</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,35 +1044,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>535</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1080,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>328675</v>
+        <v>328560</v>
       </c>
       <c r="R5" t="n">
-        <v>6397260</v>
+        <v>6397125</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1110,17 +1106,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Några kuddar på sten.</t>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,7 +1130,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1148,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120401154</v>
+        <v>120398521</v>
       </c>
       <c r="B6" t="n">
-        <v>94701</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,31 +1160,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>535</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1192,13 +1200,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>328669</v>
+        <v>328560</v>
       </c>
       <c r="R6" t="n">
-        <v>6397391</v>
+        <v>6397300</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,17 +1230,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På rotben, äldre gran. En tuva.</t>
+          <t>Kom inflygande och landade.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,7 +1259,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1260,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120398482</v>
+        <v>120401154</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>94701</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,31 +1293,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>535</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1308,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>328560</v>
+        <v>328669</v>
       </c>
       <c r="R7" t="n">
-        <v>6397125</v>
+        <v>6397391</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1338,22 +1351,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På rotben, äldre gran. En tuva.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,6 +1370,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1373,17 +1382,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Via Lars Gerre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120398521</v>
+        <v>120401028</v>
       </c>
       <c r="B8" t="n">
-        <v>57336</v>
+        <v>94701</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,39 +1401,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>535</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1432,13 +1441,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>328560</v>
+        <v>328675</v>
       </c>
       <c r="R8" t="n">
-        <v>6397300</v>
+        <v>6397260</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,27 +1471,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Kom inflygande och landade.</t>
+          <t>Några kuddar på sten.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,6 +1490,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 29826-2023 artfynd.xlsx
+++ b/artfynd/A 29826-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120398654</v>
+        <v>120401028</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>94701</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,35 +803,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>535</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>328663</v>
+        <v>328675</v>
       </c>
       <c r="R3" t="n">
-        <v>6397152</v>
+        <v>6397260</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,24 +872,14 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 2 ex.</t>
+          <t>Några kuddar på sten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,6 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -916,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120398735</v>
+        <v>120398654</v>
       </c>
       <c r="B4" t="n">
-        <v>94704</v>
+        <v>57689</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,27 +923,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>328669</v>
+        <v>328663</v>
       </c>
       <c r="R4" t="n">
-        <v>6397391</v>
+        <v>6397152</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,14 +992,24 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Några större kuddar.</t>
+          <t>Minst 2 ex.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1018,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1028,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120398482</v>
+        <v>120398521</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,20 +1048,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1061,7 +1069,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
@@ -1079,10 +1091,10 @@
         <v>328560</v>
       </c>
       <c r="R5" t="n">
-        <v>6397125</v>
+        <v>6397300</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,6 +1134,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kom inflygande och landade.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120398521</v>
+        <v>120398482</v>
       </c>
       <c r="B6" t="n">
-        <v>57336</v>
+        <v>57689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,20 +1177,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1181,11 +1198,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
@@ -1203,10 +1216,10 @@
         <v>328560</v>
       </c>
       <c r="R6" t="n">
-        <v>6397300</v>
+        <v>6397125</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,11 +1259,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Kom inflygande och landade.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1389,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120401028</v>
+        <v>120398735</v>
       </c>
       <c r="B8" t="n">
-        <v>94701</v>
+        <v>94704</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,33 +1413,25 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>535</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1441,13 +1441,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>328675</v>
+        <v>328669</v>
       </c>
       <c r="R8" t="n">
-        <v>6397260</v>
+        <v>6397391</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Några kuddar på sten.</t>
+          <t>Några större kuddar.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 29826-2023 artfynd.xlsx
+++ b/artfynd/A 29826-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120401028</v>
+        <v>120398654</v>
       </c>
       <c r="B3" t="n">
-        <v>94701</v>
+        <v>57689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,35 +803,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>535</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>328675</v>
+        <v>328663</v>
       </c>
       <c r="R3" t="n">
-        <v>6397260</v>
+        <v>6397152</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,14 +872,24 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Några kuddar på sten.</t>
+          <t>Minst 2 ex.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,7 +898,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120398654</v>
+        <v>120401028</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>94701</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,35 +932,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>535</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,13 +968,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>328663</v>
+        <v>328675</v>
       </c>
       <c r="R4" t="n">
-        <v>6397152</v>
+        <v>6397260</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,24 +1001,14 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 2 ex.</t>
+          <t>Några kuddar på sten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,6 +1017,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1036,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120398521</v>
+        <v>120401154</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>94701</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,39 +1048,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>535</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brid.) E.Britton</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1088,13 +1080,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>328560</v>
+        <v>328669</v>
       </c>
       <c r="R5" t="n">
-        <v>6397300</v>
+        <v>6397391</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,27 +1110,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kom inflygande och landade.</t>
+          <t>På rotben, äldre gran. En tuva.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,6 +1129,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1158,7 +1141,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Via Lars Gerre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1285,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120401154</v>
+        <v>120398521</v>
       </c>
       <c r="B7" t="n">
-        <v>94701</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,31 +1280,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>535</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1329,13 +1320,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>328669</v>
+        <v>328560</v>
       </c>
       <c r="R7" t="n">
-        <v>6397391</v>
+        <v>6397300</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1359,17 +1350,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På rotben, äldre gran. En tuva.</t>
+          <t>Kom inflygande och landade.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,7 +1379,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Lars Gerre</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 29826-2023 artfynd.xlsx
+++ b/artfynd/A 29826-2023 artfynd.xlsx
@@ -1148,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120398482</v>
+        <v>120398521</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,20 +1160,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1181,7 +1181,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
@@ -1199,10 +1203,10 @@
         <v>328560</v>
       </c>
       <c r="R6" t="n">
-        <v>6397125</v>
+        <v>6397300</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,6 +1246,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kom inflygande och landade.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120398521</v>
+        <v>120398482</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>57689</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,20 +1289,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1301,11 +1310,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
@@ -1323,10 +1328,10 @@
         <v>328560</v>
       </c>
       <c r="R7" t="n">
-        <v>6397300</v>
+        <v>6397125</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,11 +1371,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Kom inflygande och landade.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 29826-2023 artfynd.xlsx
+++ b/artfynd/A 29826-2023 artfynd.xlsx
@@ -1036,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120401154</v>
+        <v>120398482</v>
       </c>
       <c r="B5" t="n">
-        <v>94701</v>
+        <v>57689</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,27 +1052,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>535</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1080,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>328669</v>
+        <v>328560</v>
       </c>
       <c r="R5" t="n">
-        <v>6397391</v>
+        <v>6397125</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1110,17 +1114,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På rotben, äldre gran. En tuva.</t>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,7 +1138,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1141,7 +1149,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Lars Gerre</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1277,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120398482</v>
+        <v>120401154</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>94701</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1293,31 +1301,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>535</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1325,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>328560</v>
+        <v>328669</v>
       </c>
       <c r="R7" t="n">
-        <v>6397125</v>
+        <v>6397391</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1355,22 +1359,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På rotben, äldre gran. En tuva.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,6 +1378,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Via Lars Gerre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 29826-2023 artfynd.xlsx
+++ b/artfynd/A 29826-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120398654</v>
+        <v>120398735</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>94704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,35 +803,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>328663</v>
+        <v>328669</v>
       </c>
       <c r="R3" t="n">
-        <v>6397152</v>
+        <v>6397391</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,24 +864,14 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 2 ex.</t>
+          <t>Några större kuddar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,6 +880,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -916,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120401028</v>
+        <v>120401154</v>
       </c>
       <c r="B4" t="n">
         <v>94701</v>
@@ -949,16 +932,8 @@
           <t>(Brid.) E.Britton</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -968,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>328675</v>
+        <v>328669</v>
       </c>
       <c r="R4" t="n">
-        <v>6397260</v>
+        <v>6397391</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,7 +983,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Några kuddar på sten.</t>
+          <t>På rotben, äldre gran. En tuva.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,17 +1004,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Via Lars Gerre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120398482</v>
+        <v>120401028</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>94701</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,31 +1027,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>535</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brid.) E.Britton</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1084,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>328560</v>
+        <v>328675</v>
       </c>
       <c r="R5" t="n">
-        <v>6397125</v>
+        <v>6397260</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,22 +1093,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Några kuddar på sten.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1156,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120398521</v>
+        <v>120398654</v>
       </c>
       <c r="B6" t="n">
-        <v>57336</v>
+        <v>57689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,20 +1143,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1191,14 +1166,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1208,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>328560</v>
+        <v>328663</v>
       </c>
       <c r="R6" t="n">
-        <v>6397300</v>
+        <v>6397152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,27 +1213,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Kom inflygande och landade.</t>
+          <t>Minst 2 ex.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120401154</v>
+        <v>120398482</v>
       </c>
       <c r="B7" t="n">
-        <v>94701</v>
+        <v>57689</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,27 +1276,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>535</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1329,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>328669</v>
+        <v>328560</v>
       </c>
       <c r="R7" t="n">
-        <v>6397391</v>
+        <v>6397125</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1359,17 +1338,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På rotben, äldre gran. En tuva.</t>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,7 +1362,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1390,17 +1373,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Lars Gerre</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120398735</v>
+        <v>120398521</v>
       </c>
       <c r="B8" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,31 +1392,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1441,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>328669</v>
+        <v>328560</v>
       </c>
       <c r="R8" t="n">
-        <v>6397391</v>
+        <v>6397300</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,17 +1462,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Några större kuddar.</t>
+          <t>Kom inflygande och landade.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,7 +1491,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
